--- a/AGAP_System_Debugging_Matrix.xlsx
+++ b/AGAP_System_Debugging_Matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debugging Matrix" sheetId="1" r:id="Rbebbec4cae1345a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debugging Matrix" sheetId="1" r:id="R37394966f3c64611"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -422,7 +422,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Static code review - evidence-based findings from repository inspection. Scope: backend APIs/controllers/services, frontend controls and data flow. Runtime/database/browser integration remains pending.</x:v>
+        <x:v>Static code review - priority API access-control fixes completed on 17 Oct 2026. Runtime/database/browser integration remains pending.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -472,16 +472,16 @@
         <x:v>Only an authenticated, authorized user can delete a complaint through a POST request protected against cross-site request forgery.</x:v>
       </x:c>
       <x:c r="E5" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F5" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G5" s="17" t="str">
-        <x:v>Deletes a complaint when a GET id is supplied; starts a session but never checks user or role. A crafted link can trigger deletion for a logged-in user.</x:v>
+        <x:v>Resolved: POST-only route with Administrator/Lupon Clerk authorization, CSRF validation, integer ID validation, JSON response, and controller audit logging.</x:v>
       </x:c>
       <x:c r="H5" s="17" t="str">
-        <x:v>Require POST, enforce Administrator/Lupon Clerk authorization, add CSRF validation, validate the ID, return a JSON result, and retain an audit record before deletion.</x:v>
+        <x:v>Completed: protected POST mutation with RBAC, CSRF, ID validation, JSON result, and audit logging.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="74" customHeight="1">
@@ -498,16 +498,16 @@
         <x:v>Archive changes must be limited to authorized users and use an explicit protected mutation request.</x:v>
       </x:c>
       <x:c r="E6" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F6" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G6" s="17" t="str">
-        <x:v>Accepts an id from GET or POST, performs no role check, and archives any valid complaint. The session is not used to authorize the action.</x:v>
+        <x:v>Resolved: POST-only archive route now requires Administrator/Lupon Clerk authorization, CSRF validation, an integer complaint ID, and returns JSON.</x:v>
       </x:c>
       <x:c r="H6" s="17" t="str">
-        <x:v>Accept only POST, require the same role gate used by other complaint mutations, add CSRF protection, and reject missing or invalid IDs with 422.</x:v>
+        <x:v>Completed: protected POST archive mutation with RBAC, CSRF, ID validation, and JSON result.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="74" customHeight="1">
@@ -524,16 +524,16 @@
         <x:v>Case archival must authenticate the actor, validate the request method and case ID, and report failure accurately.</x:v>
       </x:c>
       <x:c r="E7" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F7" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G7" s="17" t="str">
-        <x:v>Reads $_POST['case_id'] directly without a method check, session initialization, authorization, or input validation. The controller audit may reference an unset session user.</x:v>
+        <x:v>Resolved: case archive route now starts a session, enforces POST, Administrator/Lupon Clerk authorization, CSRF validation, and integer case ID validation.</x:v>
       </x:c>
       <x:c r="H7" s="17" t="str">
-        <x:v>Start the session, require POST and an authorized role, validate case_id with FILTER_VALIDATE_INT, return meaningful HTTP/JSON responses, and apply CSRF protection.</x:v>
+        <x:v>Completed: protected POST archive mutation with session/RBAC, CSRF, ID validation, and JSON result.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="74" customHeight="1">
@@ -550,16 +550,16 @@
         <x:v>A save response must reflect the result of a validated, authorized controller operation.</x:v>
       </x:c>
       <x:c r="E8" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F8" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G8" s="17" t="str">
-        <x:v>Has no session or role check and always returns success after calling a non-existent SettlementController::create() method. This produces a fatal error or a false success contract depending on runtime handling.</x:v>
+        <x:v>Resolved: legacy route now calls SettlementController::save(), requires Administrator/Lupon Clerk authorization and CSRF validation, validates case_id, and propagates the controller result.</x:v>
       </x:c>
       <x:c r="H8" s="17" t="str">
-        <x:v>Retire or replace this route with SettlementController::save(), require authentication/RBAC/CSRF, validate input, and propagate the controller result and status code.</x:v>
+        <x:v>Completed: protected save route using SettlementController::save() and its returned status.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="74" customHeight="1">
@@ -576,16 +576,16 @@
         <x:v>Only authorized users can create an arbitration award and API output must reflect persistence success.</x:v>
       </x:c>
       <x:c r="E9" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F9" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G9" s="17" t="str">
-        <x:v>No session or role check; always emits a success JSON payload even if ArbitrationController::create() returns false or throws.</x:v>
+        <x:v>Resolved: legacy route now requires POST, authorized staff, CSRF validation, and a valid case ID; it reports the real persistence result.</x:v>
       </x:c>
       <x:c r="H9" s="17" t="str">
-        <x:v>Require POST, RBAC and CSRF; validate request data; inspect the controller result and return 4xx/5xx failure payloads instead of unconditional success.</x:v>
+        <x:v>Completed: protected save route with validated input and a persistence-backed JSON result.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="74" customHeight="1">
@@ -602,16 +602,16 @@
         <x:v>Sensitive complaint, party, attachment, and case data must require an authenticated authorized session.</x:v>
       </x:c>
       <x:c r="E10" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F10" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G10" s="17" t="str">
-        <x:v>Returns ComplaintController::show() without starting or checking a session. The controller includes parties, attachments, documents and workflow data.</x:v>
+        <x:v>Resolved: complaint retrieval now requires an authenticated authorized role, GET-only access, valid ID input, and an explicit not-found response.</x:v>
       </x:c>
       <x:c r="H10" s="17" t="str">
-        <x:v>Require authenticated role-based access before loading the complaint and enforce record-level authorization if access is scoped by case/team.</x:v>
+        <x:v>Completed: authenticated GET with validated ID and controlled not-found response.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="74" customHeight="1">
@@ -628,16 +628,16 @@
         <x:v>Case details should validate IDs and require an authorized reader.</x:v>
       </x:c>
       <x:c r="E11" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F11" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G11" s="17" t="str">
-        <x:v>No session/RBAC check; directly reads $_GET['id'] and returns the case controller result. An unset id also generates a PHP notice.</x:v>
+        <x:v>Resolved: case retrieval now requires an authenticated authorized role, GET-only access, valid ID input, and an explicit not-found response.</x:v>
       </x:c>
       <x:c r="H11" s="17" t="str">
-        <x:v>Start the session, validate id, return 422 for invalid input, and require an authorized role before querying the case.</x:v>
+        <x:v>Completed: authenticated GET with validated ID and controlled not-found response.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="74" customHeight="1">
@@ -654,16 +654,16 @@
         <x:v>Dashboard data should be restricted to signed-in roles and fail safely.</x:v>
       </x:c>
       <x:c r="E12" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F12" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G12" s="17" t="str">
-        <x:v>No session or role check before ReportController::dashboard() is called, exposing aggregate operational data to unauthenticated requests.</x:v>
+        <x:v>Verified: dashboard statistics already starts a session, requires an authenticated authorized role, and returns controlled error responses.</x:v>
       </x:c>
       <x:c r="H12" s="17" t="str">
-        <x:v>Apply the dashboard role gate before controller construction and use a consistent JSON error response for unauthenticated/unauthorized callers.</x:v>
+        <x:v>No change needed: the current route already implements the required authentication and controlled-error behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="74" customHeight="1">
@@ -758,16 +758,16 @@
         <x:v>Internal failure details should not be returned to clients, and scheduling constraints should be safe under concurrent requests.</x:v>
       </x:c>
       <x:c r="E16" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F16" s="17" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
-        <x:v>Exception handlers append $exception-&gt;getMessage() to the user response, leaking database or implementation details. Conflict checking occurs before persistence, so concurrent requests can both pass unless the model/database enforces the same constraint transactionally.</x:v>
+        <x:v>Resolved: detailed exceptions are logged server-side while callers receive a generic error. Scheduling and rescheduling now serialize day, venue, and presiding-officer conflict checks with database named locks before writing.</x:v>
       </x:c>
       <x:c r="H16" s="17" t="str">
-        <x:v>Log detailed exceptions server-side and return a generic message with an error ID. Enforce final conflict/capacity validation inside the write transaction and add supporting uniqueness/locking where appropriate.</x:v>
+        <x:v>Completed: transaction-level resource locks close the check-then-insert race, and client responses no longer expose internal exception details.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="74" customHeight="1">
@@ -784,16 +784,16 @@
         <x:v>Hearing schedules should not be created in the past unless an authorized exception is explicitly recorded.</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F17" s="17" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>The source explicitly states that the future date restriction is bypassed for testing/development, leaving production behavior dependent on other checks.</x:v>
+        <x:v>Resolved: server-side validation rejects any hearing date before today; the model also revalidates conflicts inside its transaction.</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>Restore server-side future-date validation with a narrowly scoped authorized override that records actor, reason, and audit history.</x:v>
+        <x:v>Completed: past dates are rejected by the server, while same-day scheduling remains subject to existing operating-hour and conflict rules.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="74" customHeight="1">
@@ -940,16 +940,16 @@
         <x:v>State-changing requests should verify a CSRF token or equivalent same-site anti-forgery mechanism.</x:v>
       </x:c>
       <x:c r="E23" s="17" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="F23" s="17" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="G23" s="17" t="str">
-        <x:v>No shared CSRF middleware or token verification was found during the endpoint review; several mutations rely only on cookies/session state.</x:v>
+        <x:v>Resolved: a shared API guard now verifies the session CSRF token for unsafe database-backed API requests. Non-database AI routes also enforce the same token. The site header automatically supplies it to same-origin fetch calls and POST forms.</x:v>
       </x:c>
       <x:c r="H23" s="17" t="str">
-        <x:v>Add a centralized CSRF token issue/validation middleware, include the token in all forms and fetch requests, and test rejection of missing/invalid tokens.</x:v>
+        <x:v>Completed: centralized CSRF enforcement prevents new database-backed mutation routes from omitting token verification; browser clients receive the token automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="74" customHeight="1">
